--- a/docs/video_manual/v1.6/exports/Master_upload_error_report.xlsx
+++ b/docs/video_manual/v1.6/exports/Master_upload_error_report.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -596,6 +596,37 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Transporters</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DM-LA2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IMPORTED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>No default rate per box - add Local_Auto_Rates rows or the rate later</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>code=DM-LA2; name=Ravi Tempo (Demo); kind=LOCAL_AUTO; methods=PER_BOX; vehicle_no=CG04-AB-1002; mobile=9000003002; city=Raipur; active=Yes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
